--- a/rutina_18_4_dias_equilibrada_casa_medio_avanzado.xlsx
+++ b/rutina_18_4_dias_equilibrada_casa_medio_avanzado.xlsx
@@ -412,11 +412,12 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="1" t="str">
-        <x:v>PLANTILLA DE ENTRENAMIENTO · TRUELIFT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2"/>
+      <x:c r="A1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PLANTILLA DE ENTRENAMIENTO · TRUELIFT</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
     <x:row r="3">
       <x:c r="A3" s="2" t="inlineStr">
         <x:is>
@@ -429,212 +430,203 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="4"/>
-    <x:row r="5"/>
     <x:row r="6">
-      <x:c r="A6" t="inlineStr">
+      <x:c r="A6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Rutina generada:</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" s="0" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Rutina 18 - 4 días - hipertrofia y fuerza equilibrada torso/pierna en casa - intermedio a avanzado</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Objetivo:</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" s="0" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Hipertrofia y fuerza con reparto equilibrado torso/pierna x2, para entrenar en casa con banco inclinable, mancuernas, barra y discos, rack y barra de dominadas.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Notas de diseño:</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B8" s="0" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Solo ejercicios compatibles con el material indicado. Los básicos usan serie top con back-off (aplica el % y RIR indicados). Las dominadas se progresan con lastre al superar el rango objetivo. Material mínimo: mancuernas, barra, discos, banco y rack. Si el rack no lleva barra de dominadas, sustituye las dominadas por «Pullover con mancuerna» o «Remo invertido» (barra en los soportes bajos) y «Elevación de piernas colgado» por «Crunch inverso». Sustitución por biblioteca: «Gemelo de pie con peso corporal» → «Gemelo a una pierna con mancuerna» para poder seguir progresando con carga.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Progresión recomendada:</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B9" s="0" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Doble progresión: cuando todas las series alcancen el techo del rango con el RIR indicado, subir carga el mínimo posible y volver al rango bajo.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Intensificadores:</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B10" s="0" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Superserie = alterna las series de los dos ejercicios enlazados sin descanso entre ellos; drop set = tras la última serie, bajadas de peso seguidas sin descanso. Cada fila admite una sola modalidad (top+back, superserie o drop set). Día 1: superserie Curl inclinado con mancuernas + Press francés con mancuernas o barra Z; drop set Elevación lateral con mancuernas (-20 %). Día 2: superserie Gemelo a una pierna con mancuerna + Elevación de piernas colgado. Día 3: superserie Fondos entre bancos + Curl martillo con mancuernas. Día 4: superserie Gemelo a una pierna con mancuerna + Crunch inverso.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Cómo usar esta plantilla (rellénala en Excel o LibreOffice):</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="inlineStr">
+    <x:row r="13">
+      <x:c r="A13" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1) Elige arriba el sistema: "simple" o "doble".</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="inlineStr">
+    <x:row r="14">
+      <x:c r="A14" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">2) En cada pestaña Día 1..Día 5: nombre de la sesión (B1) y ejercicios.</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="inlineStr">
+    <x:row r="15">
+      <x:c r="A15" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">3) Elige PATRÓN (A) y, según el patrón, el EJERCICIO (B).</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="inlineStr">
+    <x:row r="16">
+      <x:c r="A16" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">   Indica SERIES, RIR objetivo y repeticiones.</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" t="inlineStr">
+    <x:row r="17">
+      <x:c r="A17" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">   - SIMPLE: solo "Reps mín / objetivo".</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="12">
-      <x:c r="A12" t="inlineStr">
+    <x:row r="18">
+      <x:c r="A18" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">   - DOBLE: "Reps mín" y "Reps máx".</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="13">
-      <x:c r="A13" t="inlineStr">
+    <x:row r="19">
+      <x:c r="A19" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">4) DESCANSO (min): admite medios minutos (0,5).</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="inlineStr">
+    <x:row r="20">
+      <x:c r="A20" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">5) Deja el PATRÓN en "(Ninguno)" en las filas que no uses.</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="15">
-      <x:c r="A15" t="inlineStr">
+    <x:row r="21">
+      <x:c r="A21" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">6) Usa entre 2 y 5 días.</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="16">
-      <x:c r="A16" t="inlineStr">
+    <x:row r="22">
+      <x:c r="A22" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">7) Guarda y pulsa "Importar" en la app.</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="17">
-      <x:c r="A17" t="inlineStr">
+    <x:row r="23">
+      <x:c r="A23" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">8) TOP+BACK (opcional, columna H) = "sí": la 1.ª serie es la top</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18" t="inlineStr">
+    <x:row r="24">
+      <x:c r="A24" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">   (fija la progresión) y el resto back-offs con el % menos de peso (I)</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="19">
-      <x:c r="A19" t="inlineStr">
+    <x:row r="25">
+      <x:c r="A25" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">   hasta el RIR de la columna J. Vacío o "no" = series rectas.</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="20">
-      <x:c r="A20" t="inlineStr">
+    <x:row r="26">
+      <x:c r="A26" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">9) SUPERSERIE (columna K): pon el mismo número (1, 2…) en dos filas</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="21">
-      <x:c r="A21" t="inlineStr">
+    <x:row r="27">
+      <x:c r="A27" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">   seguidas para enlazarlas y alternar sus series sin descanso.</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="22">
-      <x:c r="A22" t="inlineStr">
+    <x:row r="28">
+      <x:c r="A28" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">10) DROP SET (columna L) = "sí": tras la última serie, bajadas de peso</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="23">
-      <x:c r="A23" t="inlineStr">
+    <x:row r="29">
+      <x:c r="A29" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">    seguidas del % de la columna M, sin descanso.</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="24">
-      <x:c r="A24" t="inlineStr">
+    <x:row r="30">
+      <x:c r="A30" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">11) Cada fila admite solo UNA modalidad: top+back, drop set o superserie;</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="25">
-      <x:c r="A25" t="inlineStr">
+    <x:row r="31">
+      <x:c r="A31" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">    el Excel bloquea las combinaciones y la app deshace las que lleguen.</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FICHA DE LA RUTINA</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Rutina generada:</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B28" s="0" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Rutina 18 - 4 días - hipertrofia y fuerza equilibrada torso/pierna en casa - intermedio a avanzado</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Objetivo:</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B29" s="0" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Hipertrofia y fuerza con reparto equilibrado torso/pierna x2, para entrenar en casa con banco inclinable, mancuernas, barra y discos, rack y barra de dominadas.</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Notas de diseño:</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B30" s="0" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Solo ejercicios compatibles con el material indicado. Los básicos usan serie top con back-off (aplica el % y RIR indicados). Las dominadas se progresan con lastre al superar el rango objetivo. Material mínimo: mancuernas, barra, discos, banco y rack. Si el rack no lleva barra de dominadas, sustituye las dominadas por «Pullover con mancuerna» o «Remo invertido» (barra en los soportes bajos) y «Elevación de piernas colgado» por «Crunch inverso». Sustitución por biblioteca: «Gemelo de pie con peso corporal» → «Gemelo a una pierna con mancuerna» para poder seguir progresando con carga.</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Progresión recomendada:</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B31" s="0" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Doble progresión: cuando todas las series alcancen el techo del rango con el RIR indicado, subir carga el mínimo posible y volver al rango bajo.</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Intensificadores:</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B32" s="0" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Superserie = alterna las series de los dos ejercicios enlazados sin descanso entre ellos; drop set = tras la última serie, bajadas de peso seguidas sin descanso. Cada fila admite una sola modalidad (top+back, superserie o drop set). Día 1: superserie Curl inclinado con mancuernas + Press francés con mancuernas o barra Z; drop set Elevación lateral con mancuernas (-20 %). Día 2: superserie Gemelo a una pierna con mancuerna + Elevación de piernas colgado. Día 3: superserie Fondos entre bancos + Curl martillo con mancuernas. Día 4: superserie Gemelo a una pierna con mancuerna + Crunch inverso.</x:t>
         </x:is>
       </x:c>
     </x:row>
